--- a/Project/data/Data/2_China's_EX_Reserves.xlsx
+++ b/Project/data/Data/2_China's_EX_Reserves.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karry/KarryRen/Fintech/Karry-PHBS/FintechClass/Class/M2/Financial-Market-and-Investment-in-China/FMIC/Project/data/Data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE35678-A807-8049-9D5D-863E91FA428E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="630" windowWidth="27495" windowHeight="13950"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="China's Official Fox Reserves" sheetId="1" r:id="rId1"/>
@@ -14,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>数据来源：Wind</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -30,16 +33,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -51,7 +54,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -91,13 +94,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -116,8 +119,2646 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'China''s Official Fox Reserves'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>China's Official Fox Reserves(Hundred Millon $)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'China''s Official Fox Reserves'!$A$2:$A$333</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm</c:formatCode>
+                <c:ptCount val="332"/>
+                <c:pt idx="0">
+                  <c:v>36556</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36585</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36616</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36646</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36677</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36707</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36738</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36769</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36799</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36830</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36860</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36891</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36922</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36950</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>36981</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>37011</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>37042</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>37072</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37103</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>37134</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>37164</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>37195</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>37225</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>37256</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>37287</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>37315</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>37346</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>37376</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>37407</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>37437</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>37468</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>37499</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>37529</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>37560</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>37590</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>37621</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37652</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37680</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>37711</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>37741</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>37772</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>37802</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>37833</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>37864</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>37894</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>37925</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>37955</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>37986</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>38017</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>38046</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>38077</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>38107</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>38138</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>38168</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>38199</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>38230</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>38260</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>38291</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>38321</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>38352</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>38383</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>38411</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>38442</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>38472</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>38503</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>38533</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>38564</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>38595</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>38625</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>38656</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>38686</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>38717</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>38748</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>38776</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>38807</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>38837</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>38868</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>38898</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>38929</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>38960</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>38990</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>39021</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>39051</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>39082</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>39113</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>39141</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>39172</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>39202</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>39233</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>39263</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>39294</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>39325</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>39355</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>39386</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>39416</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>39447</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>39478</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>39507</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>39538</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>39568</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>39599</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>39629</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>39660</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>39691</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>39721</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>39752</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>39782</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>39813</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>39844</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>39872</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>39903</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>39933</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>39964</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>39994</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>40025</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>40056</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>40086</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>40117</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>40147</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>40178</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>40209</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>40237</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>40268</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>40298</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>40329</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>40359</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>40390</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>40421</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>40451</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>40482</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>40512</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>40543</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>40574</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>40602</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>40633</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>40663</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>40694</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>40724</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>40755</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>40786</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>40816</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>40847</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>40877</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>40908</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>40939</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>40968</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>40999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>41029</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>41060</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>41090</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>41121</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>41152</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>41182</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>41213</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>41243</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>41274</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>41305</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>41333</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>41364</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>41394</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>41425</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>41455</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>41486</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>41517</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>41547</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>41578</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>41608</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>41639</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>41670</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>41698</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>41729</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>41759</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>41790</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>41820</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>41851</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>41882</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>41912</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>41943</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>41973</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>42004</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>42035</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>42063</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>42094</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>42124</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>42155</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>42185</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>42216</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>42247</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>42277</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>42308</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>42338</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>42369</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>42400</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>42429</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>42460</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>42490</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>42521</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>42551</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>42582</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>42613</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>42643</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>42674</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>42704</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>42735</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>42766</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>42794</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>42825</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>42855</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>42886</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>42916</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>42947</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>42978</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>43008</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>43039</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>43069</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>43100</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>43131</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>43159</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>43190</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>43220</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>43251</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>43281</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>43312</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>43343</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>43373</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>43404</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>43434</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>43465</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>43496</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>43524</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>43555</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>43585</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>43616</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>43646</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>43677</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>43708</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>43738</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>43769</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>43799</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>43830</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>43861</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>43890</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>43921</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>43951</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>43982</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>44012</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>44043</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>44074</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>44104</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>44135</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>44165</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>44196</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>44227</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>44255</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>44286</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>44316</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>44347</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>44377</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>44408</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>44439</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>44469</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>44500</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>44530</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>44561</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>44592</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>44620</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>44651</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>44681</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>44712</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>44742</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>44773</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>44804</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>44834</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>44865</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>44895</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>44926</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>44957</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>44985</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>45016</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>45046</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>45077</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>45107</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>45138</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>45169</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>45199</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>45230</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>45260</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>45291</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>45322</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>45351</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>45382</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>45412</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>45443</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>45473</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>45504</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>45535</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>45596</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>45626</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'China''s Official Fox Reserves'!$B$2:$B$333</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00_ </c:formatCode>
+                <c:ptCount val="332"/>
+                <c:pt idx="0">
+                  <c:v>1561</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1565.59</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1568.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1568.46</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1580.19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1585.6799999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1585.96</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1592.17</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1600.92</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1613.4399999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1639.11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1655.74</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1686.23</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1747.73</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1758.47</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1771.78</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1790</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1808.38</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1844.92</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1900.53</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1957.6399999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2030.2900000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2083.15</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2121.65</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2174</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2235.31</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2276.0500000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2338.2400000000002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2384.73</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2427.63</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2465.34</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2530.9</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2586.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2655.3900000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2746.25</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2864.0699999999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3044.6</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3082.5</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3160.1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3262.9100000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3400.61</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3464.76</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3564.86</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3647.34</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3838.63</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4009.9199999999996</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4203.6100000000006</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4032.5099999999998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4157.2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4266.3999999999996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4398.22</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4490.17</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4585.5999999999995</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>4706.3900000000003</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4829.8200000000006</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4961.6900000000005</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5145.38</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5424.43</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5738.8200000000006</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6099.32</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6236.46</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6426.0999999999995</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6591.4400000000005</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6707.74</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6910.12</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>7109.7300000000005</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7327.33</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>7532.09</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>7690.0400000000009</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7849.02</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7942.2300000000005</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>8188.72</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>8451.7999999999993</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8536.7199999999993</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>8750.6999999999989</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>8950.4</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9250.1999999999989</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9411.1500000000015</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>9545.5</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>9720.39</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>9879.2800000000007</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>10096.26</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>10387.51</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>10663.44</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>11046.92</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>11573.720000000001</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>12020.31</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>12465.66</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>12926.710000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>13326.247100000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>13851.998100000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>14086.411900000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>14336.114</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>14548.9792</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>14969.058299999999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>15282.491100000001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>15898.1</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>16471.34</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>16821.77</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>17566.55</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>17969.61</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>18088.28</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>18451.64</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>18841.53</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>19055.850000000002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>18796.875599999999</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>18847.173200000001</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>19460.3024</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>19134.559999999998</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>19120.66</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>19537.41</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>20088.8</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>20894.91</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>21316.06</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>21746.18</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>22108.27</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>22725.95</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>23282.720000000001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>23887.884699999999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>23991.5229</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>24152.2107</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>24245.9067</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>24470.836500000001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>24905.116999999998</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>24395.057799999999</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>24542.748</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>25388.9395</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>25478.377100000002</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>26483.03</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>27608.99</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>27678.09</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>28473.38</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>29316.74</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>29913.86</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>30446.74</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>31458.430000000004</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>31659.969999999998</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>31974.91</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>32452.83</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>32624.989999999998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>32016.829999999998</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>32737.96</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>32209.07</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>31811.479999999996</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>32536.31</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>33096.57</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>33049.71</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>32989.129999999997</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>32061.089999999997</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>32400.05</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>32399.52</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>32729.01</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>32850.950000000004</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>32874.26</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>32976.71</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>33115.89</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>34100.61</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>33954.18</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>34426.49</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>35344.82</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>35148.07</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>34966.86</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>35478.1</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>35530.43</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>36626.620000000003</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>37365.870000000003</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>37894.509999999995</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>38213.15</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>38666.410000000003</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>39137.39</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>39480.97</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>39787.950000000004</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>39838.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>39932.130000000005</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>39662.67</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>39688.25</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>38877</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>38529.18</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>38473.54</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>38430.18</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>38134.14</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>38015.03</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>37300.380000000005</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>37481.42</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>37111.43</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>36938.379999999997</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>36513.1</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>35573.81</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>35141.200000000004</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>35255.07</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>34382.840000000004</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>33303.620000000003</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>32308.929999999997</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>32023.210000000003</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>32125.79</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>32196.68</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>31917.360000000001</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>32051.620000000003</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>32010.570000000003</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>31851.670000000002</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>31663.82</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>31206.55</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>30515.98</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>30105.17</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>29982.039999999997</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>30051.24</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>30090.880000000001</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>30295.33</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>30535.670000000002</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>30567.89</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>30807.200000000001</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>30915.27</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>31085.1</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>31092.13</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>31192.77</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>31399.489999999998</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>31614.57</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>31344.820000000003</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>31428.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>31248.520000000004</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>31106.23</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>31121.29</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>31179.460000000003</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>31097.16</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>30870.25</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>30530.979999999996</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>30616.969999999998</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>30727.119999999999</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>30879.24</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>30901.8</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>30987.61</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>30949.53</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>31010.04</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>31192.34</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>31036.97</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>31071.759999999998</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>30924.31</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>31051.61</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>30955.910000000003</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>31079.24</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>31154.97</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>31067.179999999997</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>30606.33</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>30914.59</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>31016.920000000002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>31123.279999999999</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>31543.91</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>31646.09</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>31425.620000000003</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>31279.819999999996</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>31784.9</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>32165.219999999998</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>32106.71</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>32049.940000000002</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>31700.289999999997</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>31981.8</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>32218.03</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>32140.1</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>32358.9</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>32321.16</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>32006.26</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>32176.140000000003</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>32223.86</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>32501.66</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>32216.320000000003</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>32138.27</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>31879.940000000002</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>31197.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>31277.800000000003</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>30712.720000000001</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>31040.71</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>30548.809999999998</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>30289.55</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>30524.269999999997</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>31174.880000000001</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>31276.91</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>31844.62</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>31331.530000000002</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>31838.720000000001</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>32047.66</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>31765.08</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>31929.98</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>32042.7</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>31600.98</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>31150.699999999997</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>31012.239999999998</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>31718.07</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>32379.770000000004</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>32193.200000000001</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>32258.17</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>32456.57</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>32008.309999999998</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>32320.39</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>32223.579999999998</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>32563.72</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>32882.15</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>33163.67</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>32610.499999999996</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>32658.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-77B1-684F-9300-60F370FC151A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="867259487"/>
+        <c:axId val="1128157920"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="867259487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128157920"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+        <c:majorUnit val="12"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1128157920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="867259487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3556000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C0A5757-E4DC-A640-8DCE-5BA14D58EB7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -163,7 +2804,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -196,9 +2837,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -231,6 +2889,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -406,23 +3081,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B333"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="56.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="56.1640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" ht="16.5" customHeight="1">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="3">
         <v>36556</v>
       </c>
@@ -430,7 +3105,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2">
       <c r="A3" s="3">
         <v>36585</v>
       </c>
@@ -438,7 +3113,7 @@
         <v>1565.59</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2">
       <c r="A4" s="3">
         <v>36616</v>
       </c>
@@ -446,7 +3121,7 @@
         <v>1568.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2">
       <c r="A5" s="3">
         <v>36646</v>
       </c>
@@ -454,7 +3129,7 @@
         <v>1568.46</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2">
       <c r="A6" s="3">
         <v>36677</v>
       </c>
@@ -462,7 +3137,7 @@
         <v>1580.19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2">
       <c r="A7" s="3">
         <v>36707</v>
       </c>
@@ -470,7 +3145,7 @@
         <v>1585.6799999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2">
       <c r="A8" s="3">
         <v>36738</v>
       </c>
@@ -478,7 +3153,7 @@
         <v>1585.96</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2">
       <c r="A9" s="3">
         <v>36769</v>
       </c>
@@ -486,7 +3161,7 @@
         <v>1592.17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="14.25" customHeight="1">
       <c r="A10" s="3">
         <v>36799</v>
       </c>
@@ -494,7 +3169,7 @@
         <v>1600.92</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2">
       <c r="A11" s="3">
         <v>36830</v>
       </c>
@@ -502,7 +3177,7 @@
         <v>1613.4399999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2">
       <c r="A12" s="3">
         <v>36860</v>
       </c>
@@ -510,7 +3185,7 @@
         <v>1639.11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2">
       <c r="A13" s="3">
         <v>36891</v>
       </c>
@@ -518,7 +3193,7 @@
         <v>1655.74</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2">
       <c r="A14" s="3">
         <v>36922</v>
       </c>
@@ -526,7 +3201,7 @@
         <v>1686.23</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2">
       <c r="A15" s="3">
         <v>36950</v>
       </c>
@@ -534,7 +3209,7 @@
         <v>1747.73</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2">
       <c r="A16" s="3">
         <v>36981</v>
       </c>
@@ -542,7 +3217,7 @@
         <v>1758.47</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2">
       <c r="A17" s="3">
         <v>37011</v>
       </c>
@@ -550,7 +3225,7 @@
         <v>1771.78</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:2">
       <c r="A18" s="3">
         <v>37042</v>
       </c>
@@ -558,7 +3233,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:2">
       <c r="A19" s="3">
         <v>37072</v>
       </c>
@@ -566,7 +3241,7 @@
         <v>1808.38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:2">
       <c r="A20" s="3">
         <v>37103</v>
       </c>
@@ -574,7 +3249,7 @@
         <v>1844.92</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:2">
       <c r="A21" s="3">
         <v>37134</v>
       </c>
@@ -582,7 +3257,7 @@
         <v>1900.53</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:2">
       <c r="A22" s="3">
         <v>37164</v>
       </c>
@@ -590,7 +3265,7 @@
         <v>1957.6399999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:2">
       <c r="A23" s="3">
         <v>37195</v>
       </c>
@@ -598,7 +3273,7 @@
         <v>2030.2900000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:2">
       <c r="A24" s="3">
         <v>37225</v>
       </c>
@@ -606,7 +3281,7 @@
         <v>2083.15</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:2">
       <c r="A25" s="3">
         <v>37256</v>
       </c>
@@ -614,7 +3289,7 @@
         <v>2121.65</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:2">
       <c r="A26" s="3">
         <v>37287</v>
       </c>
@@ -622,7 +3297,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:2">
       <c r="A27" s="3">
         <v>37315</v>
       </c>
@@ -630,7 +3305,7 @@
         <v>2235.31</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:2">
       <c r="A28" s="3">
         <v>37346</v>
       </c>
@@ -638,7 +3313,7 @@
         <v>2276.0500000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:2">
       <c r="A29" s="3">
         <v>37376</v>
       </c>
@@ -646,7 +3321,7 @@
         <v>2338.2400000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:2">
       <c r="A30" s="3">
         <v>37407</v>
       </c>
@@ -654,7 +3329,7 @@
         <v>2384.73</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:2">
       <c r="A31" s="3">
         <v>37437</v>
       </c>
@@ -662,7 +3337,7 @@
         <v>2427.63</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:2">
       <c r="A32" s="3">
         <v>37468</v>
       </c>
@@ -670,7 +3345,7 @@
         <v>2465.34</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:2">
       <c r="A33" s="3">
         <v>37499</v>
       </c>
@@ -678,7 +3353,7 @@
         <v>2530.9</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:2">
       <c r="A34" s="3">
         <v>37529</v>
       </c>
@@ -686,7 +3361,7 @@
         <v>2586.3000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:2">
       <c r="A35" s="3">
         <v>37560</v>
       </c>
@@ -694,7 +3369,7 @@
         <v>2655.3900000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:2">
       <c r="A36" s="3">
         <v>37590</v>
       </c>
@@ -702,7 +3377,7 @@
         <v>2746.25</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:2">
       <c r="A37" s="3">
         <v>37621</v>
       </c>
@@ -710,7 +3385,7 @@
         <v>2864.0699999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:2">
       <c r="A38" s="3">
         <v>37652</v>
       </c>
@@ -718,7 +3393,7 @@
         <v>3044.6</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:2">
       <c r="A39" s="3">
         <v>37680</v>
       </c>
@@ -726,7 +3401,7 @@
         <v>3082.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:2">
       <c r="A40" s="3">
         <v>37711</v>
       </c>
@@ -734,7 +3409,7 @@
         <v>3160.1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:2">
       <c r="A41" s="3">
         <v>37741</v>
       </c>
@@ -742,7 +3417,7 @@
         <v>3262.9100000000003</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:2">
       <c r="A42" s="3">
         <v>37772</v>
       </c>
@@ -750,7 +3425,7 @@
         <v>3400.61</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:2">
       <c r="A43" s="3">
         <v>37802</v>
       </c>
@@ -758,7 +3433,7 @@
         <v>3464.76</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:2">
       <c r="A44" s="3">
         <v>37833</v>
       </c>
@@ -766,7 +3441,7 @@
         <v>3564.86</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:2">
       <c r="A45" s="3">
         <v>37864</v>
       </c>
@@ -774,7 +3449,7 @@
         <v>3647.34</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:2">
       <c r="A46" s="3">
         <v>37894</v>
       </c>
@@ -782,7 +3457,7 @@
         <v>3838.63</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:2">
       <c r="A47" s="3">
         <v>37925</v>
       </c>
@@ -790,7 +3465,7 @@
         <v>4009.9199999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:2">
       <c r="A48" s="3">
         <v>37955</v>
       </c>
@@ -798,7 +3473,7 @@
         <v>4203.6100000000006</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:2">
       <c r="A49" s="3">
         <v>37986</v>
       </c>
@@ -806,7 +3481,7 @@
         <v>4032.5099999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:2">
       <c r="A50" s="3">
         <v>38017</v>
       </c>
@@ -814,7 +3489,7 @@
         <v>4157.2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:2">
       <c r="A51" s="3">
         <v>38046</v>
       </c>
@@ -822,7 +3497,7 @@
         <v>4266.3999999999996</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:2">
       <c r="A52" s="3">
         <v>38077</v>
       </c>
@@ -830,7 +3505,7 @@
         <v>4398.22</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:2">
       <c r="A53" s="3">
         <v>38107</v>
       </c>
@@ -838,7 +3513,7 @@
         <v>4490.17</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:2">
       <c r="A54" s="3">
         <v>38138</v>
       </c>
@@ -846,7 +3521,7 @@
         <v>4585.5999999999995</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:2">
       <c r="A55" s="3">
         <v>38168</v>
       </c>
@@ -854,7 +3529,7 @@
         <v>4706.3900000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:2">
       <c r="A56" s="3">
         <v>38199</v>
       </c>
@@ -862,7 +3537,7 @@
         <v>4829.8200000000006</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:2">
       <c r="A57" s="3">
         <v>38230</v>
       </c>
@@ -870,7 +3545,7 @@
         <v>4961.6900000000005</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:2">
       <c r="A58" s="3">
         <v>38260</v>
       </c>
@@ -878,7 +3553,7 @@
         <v>5145.38</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:2">
       <c r="A59" s="3">
         <v>38291</v>
       </c>
@@ -886,7 +3561,7 @@
         <v>5424.43</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:2">
       <c r="A60" s="3">
         <v>38321</v>
       </c>
@@ -894,7 +3569,7 @@
         <v>5738.8200000000006</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:2">
       <c r="A61" s="3">
         <v>38352</v>
       </c>
@@ -902,7 +3577,7 @@
         <v>6099.32</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:2">
       <c r="A62" s="3">
         <v>38383</v>
       </c>
@@ -910,7 +3585,7 @@
         <v>6236.46</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:2">
       <c r="A63" s="3">
         <v>38411</v>
       </c>
@@ -918,7 +3593,7 @@
         <v>6426.0999999999995</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:2">
       <c r="A64" s="3">
         <v>38442</v>
       </c>
@@ -926,7 +3601,7 @@
         <v>6591.4400000000005</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:2">
       <c r="A65" s="3">
         <v>38472</v>
       </c>
@@ -934,7 +3609,7 @@
         <v>6707.74</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:2">
       <c r="A66" s="3">
         <v>38503</v>
       </c>
@@ -942,7 +3617,7 @@
         <v>6910.12</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:2">
       <c r="A67" s="3">
         <v>38533</v>
       </c>
@@ -950,7 +3625,7 @@
         <v>7109.7300000000005</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:2">
       <c r="A68" s="3">
         <v>38564</v>
       </c>
@@ -958,7 +3633,7 @@
         <v>7327.33</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:2">
       <c r="A69" s="3">
         <v>38595</v>
       </c>
@@ -966,7 +3641,7 @@
         <v>7532.09</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:2">
       <c r="A70" s="3">
         <v>38625</v>
       </c>
@@ -974,7 +3649,7 @@
         <v>7690.0400000000009</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:2">
       <c r="A71" s="3">
         <v>38656</v>
       </c>
@@ -982,7 +3657,7 @@
         <v>7849.02</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:2">
       <c r="A72" s="3">
         <v>38686</v>
       </c>
@@ -990,7 +3665,7 @@
         <v>7942.2300000000005</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:2">
       <c r="A73" s="3">
         <v>38717</v>
       </c>
@@ -998,7 +3673,7 @@
         <v>8188.72</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:2">
       <c r="A74" s="3">
         <v>38748</v>
       </c>
@@ -1006,7 +3681,7 @@
         <v>8451.7999999999993</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:2">
       <c r="A75" s="3">
         <v>38776</v>
       </c>
@@ -1014,7 +3689,7 @@
         <v>8536.7199999999993</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:2">
       <c r="A76" s="3">
         <v>38807</v>
       </c>
@@ -1022,7 +3697,7 @@
         <v>8750.6999999999989</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:2">
       <c r="A77" s="3">
         <v>38837</v>
       </c>
@@ -1030,7 +3705,7 @@
         <v>8950.4</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:2">
       <c r="A78" s="3">
         <v>38868</v>
       </c>
@@ -1038,7 +3713,7 @@
         <v>9250.1999999999989</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:2">
       <c r="A79" s="3">
         <v>38898</v>
       </c>
@@ -1046,7 +3721,7 @@
         <v>9411.1500000000015</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:2">
       <c r="A80" s="3">
         <v>38929</v>
       </c>
@@ -1054,7 +3729,7 @@
         <v>9545.5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:2">
       <c r="A81" s="3">
         <v>38960</v>
       </c>
@@ -1062,7 +3737,7 @@
         <v>9720.39</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:2">
       <c r="A82" s="3">
         <v>38990</v>
       </c>
@@ -1070,7 +3745,7 @@
         <v>9879.2800000000007</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:2">
       <c r="A83" s="3">
         <v>39021</v>
       </c>
@@ -1078,7 +3753,7 @@
         <v>10096.26</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:2">
       <c r="A84" s="3">
         <v>39051</v>
       </c>
@@ -1086,7 +3761,7 @@
         <v>10387.51</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:2">
       <c r="A85" s="3">
         <v>39082</v>
       </c>
@@ -1094,7 +3769,7 @@
         <v>10663.44</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:2">
       <c r="A86" s="3">
         <v>39113</v>
       </c>
@@ -1102,7 +3777,7 @@
         <v>11046.92</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:2">
       <c r="A87" s="3">
         <v>39141</v>
       </c>
@@ -1110,7 +3785,7 @@
         <v>11573.720000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:2">
       <c r="A88" s="3">
         <v>39172</v>
       </c>
@@ -1118,7 +3793,7 @@
         <v>12020.31</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:2">
       <c r="A89" s="3">
         <v>39202</v>
       </c>
@@ -1126,7 +3801,7 @@
         <v>12465.66</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:2">
       <c r="A90" s="3">
         <v>39233</v>
       </c>
@@ -1134,7 +3809,7 @@
         <v>12926.710000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:2">
       <c r="A91" s="3">
         <v>39263</v>
       </c>
@@ -1142,7 +3817,7 @@
         <v>13326.247100000001</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:2">
       <c r="A92" s="3">
         <v>39294</v>
       </c>
@@ -1150,7 +3825,7 @@
         <v>13851.998100000001</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:2">
       <c r="A93" s="3">
         <v>39325</v>
       </c>
@@ -1158,7 +3833,7 @@
         <v>14086.411900000001</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:2">
       <c r="A94" s="3">
         <v>39355</v>
       </c>
@@ -1166,7 +3841,7 @@
         <v>14336.114</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:2">
       <c r="A95" s="3">
         <v>39386</v>
       </c>
@@ -1174,7 +3849,7 @@
         <v>14548.9792</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:2">
       <c r="A96" s="3">
         <v>39416</v>
       </c>
@@ -1182,7 +3857,7 @@
         <v>14969.058299999999</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:2">
       <c r="A97" s="3">
         <v>39447</v>
       </c>
@@ -1190,7 +3865,7 @@
         <v>15282.491100000001</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:2">
       <c r="A98" s="3">
         <v>39478</v>
       </c>
@@ -1198,7 +3873,7 @@
         <v>15898.1</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:2">
       <c r="A99" s="3">
         <v>39507</v>
       </c>
@@ -1206,7 +3881,7 @@
         <v>16471.34</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:2">
       <c r="A100" s="3">
         <v>39538</v>
       </c>
@@ -1214,7 +3889,7 @@
         <v>16821.77</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:2">
       <c r="A101" s="3">
         <v>39568</v>
       </c>
@@ -1222,7 +3897,7 @@
         <v>17566.55</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:2">
       <c r="A102" s="3">
         <v>39599</v>
       </c>
@@ -1230,7 +3905,7 @@
         <v>17969.61</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:2">
       <c r="A103" s="3">
         <v>39629</v>
       </c>
@@ -1238,7 +3913,7 @@
         <v>18088.28</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:2">
       <c r="A104" s="3">
         <v>39660</v>
       </c>
@@ -1246,7 +3921,7 @@
         <v>18451.64</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:2">
       <c r="A105" s="3">
         <v>39691</v>
       </c>
@@ -1254,7 +3929,7 @@
         <v>18841.53</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:2">
       <c r="A106" s="3">
         <v>39721</v>
       </c>
@@ -1262,7 +3937,7 @@
         <v>19055.850000000002</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:2">
       <c r="A107" s="3">
         <v>39752</v>
       </c>
@@ -1270,7 +3945,7 @@
         <v>18796.875599999999</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:2">
       <c r="A108" s="3">
         <v>39782</v>
       </c>
@@ -1278,7 +3953,7 @@
         <v>18847.173200000001</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:2">
       <c r="A109" s="3">
         <v>39813</v>
       </c>
@@ -1286,7 +3961,7 @@
         <v>19460.3024</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:2">
       <c r="A110" s="3">
         <v>39844</v>
       </c>
@@ -1294,7 +3969,7 @@
         <v>19134.559999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:2">
       <c r="A111" s="3">
         <v>39872</v>
       </c>
@@ -1302,7 +3977,7 @@
         <v>19120.66</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:2">
       <c r="A112" s="3">
         <v>39903</v>
       </c>
@@ -1310,7 +3985,7 @@
         <v>19537.41</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:2">
       <c r="A113" s="3">
         <v>39933</v>
       </c>
@@ -1318,7 +3993,7 @@
         <v>20088.8</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:2">
       <c r="A114" s="3">
         <v>39964</v>
       </c>
@@ -1326,7 +4001,7 @@
         <v>20894.91</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:2">
       <c r="A115" s="3">
         <v>39994</v>
       </c>
@@ -1334,7 +4009,7 @@
         <v>21316.06</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:2">
       <c r="A116" s="3">
         <v>40025</v>
       </c>
@@ -1342,7 +4017,7 @@
         <v>21746.18</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:2">
       <c r="A117" s="3">
         <v>40056</v>
       </c>
@@ -1350,7 +4025,7 @@
         <v>22108.27</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:2">
       <c r="A118" s="3">
         <v>40086</v>
       </c>
@@ -1358,7 +4033,7 @@
         <v>22725.95</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:2">
       <c r="A119" s="3">
         <v>40117</v>
       </c>
@@ -1366,7 +4041,7 @@
         <v>23282.720000000001</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:2">
       <c r="A120" s="3">
         <v>40147</v>
       </c>
@@ -1374,7 +4049,7 @@
         <v>23887.884699999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:2">
       <c r="A121" s="3">
         <v>40178</v>
       </c>
@@ -1382,7 +4057,7 @@
         <v>23991.5229</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:2">
       <c r="A122" s="3">
         <v>40209</v>
       </c>
@@ -1390,7 +4065,7 @@
         <v>24152.2107</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:2">
       <c r="A123" s="3">
         <v>40237</v>
       </c>
@@ -1398,7 +4073,7 @@
         <v>24245.9067</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:2">
       <c r="A124" s="3">
         <v>40268</v>
       </c>
@@ -1406,7 +4081,7 @@
         <v>24470.836500000001</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:2">
       <c r="A125" s="3">
         <v>40298</v>
       </c>
@@ -1414,7 +4089,7 @@
         <v>24905.116999999998</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:2">
       <c r="A126" s="3">
         <v>40329</v>
       </c>
@@ -1422,7 +4097,7 @@
         <v>24395.057799999999</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:2">
       <c r="A127" s="3">
         <v>40359</v>
       </c>
@@ -1430,7 +4105,7 @@
         <v>24542.748</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:2">
       <c r="A128" s="3">
         <v>40390</v>
       </c>
@@ -1438,7 +4113,7 @@
         <v>25388.9395</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:2">
       <c r="A129" s="3">
         <v>40421</v>
       </c>
@@ -1446,7 +4121,7 @@
         <v>25478.377100000002</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:2">
       <c r="A130" s="3">
         <v>40451</v>
       </c>
@@ -1454,7 +4129,7 @@
         <v>26483.03</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:2">
       <c r="A131" s="3">
         <v>40482</v>
       </c>
@@ -1462,7 +4137,7 @@
         <v>27608.99</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:2">
       <c r="A132" s="3">
         <v>40512</v>
       </c>
@@ -1470,7 +4145,7 @@
         <v>27678.09</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:2">
       <c r="A133" s="3">
         <v>40543</v>
       </c>
@@ -1478,7 +4153,7 @@
         <v>28473.38</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:2">
       <c r="A134" s="3">
         <v>40574</v>
       </c>
@@ -1486,7 +4161,7 @@
         <v>29316.74</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:2">
       <c r="A135" s="3">
         <v>40602</v>
       </c>
@@ -1494,7 +4169,7 @@
         <v>29913.86</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:2">
       <c r="A136" s="3">
         <v>40633</v>
       </c>
@@ -1502,7 +4177,7 @@
         <v>30446.74</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:2">
       <c r="A137" s="3">
         <v>40663</v>
       </c>
@@ -1510,7 +4185,7 @@
         <v>31458.430000000004</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:2">
       <c r="A138" s="3">
         <v>40694</v>
       </c>
@@ -1518,7 +4193,7 @@
         <v>31659.969999999998</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:2">
       <c r="A139" s="3">
         <v>40724</v>
       </c>
@@ -1526,7 +4201,7 @@
         <v>31974.91</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:2">
       <c r="A140" s="3">
         <v>40755</v>
       </c>
@@ -1534,7 +4209,7 @@
         <v>32452.83</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:2">
       <c r="A141" s="3">
         <v>40786</v>
       </c>
@@ -1542,7 +4217,7 @@
         <v>32624.989999999998</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:2">
       <c r="A142" s="3">
         <v>40816</v>
       </c>
@@ -1550,7 +4225,7 @@
         <v>32016.829999999998</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:2">
       <c r="A143" s="3">
         <v>40847</v>
       </c>
@@ -1558,7 +4233,7 @@
         <v>32737.96</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:2">
       <c r="A144" s="3">
         <v>40877</v>
       </c>
@@ -1566,7 +4241,7 @@
         <v>32209.07</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:2">
       <c r="A145" s="3">
         <v>40908</v>
       </c>
@@ -1574,7 +4249,7 @@
         <v>31811.479999999996</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:2">
       <c r="A146" s="3">
         <v>40939</v>
       </c>
@@ -1582,7 +4257,7 @@
         <v>32536.31</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:2">
       <c r="A147" s="3">
         <v>40968</v>
       </c>
@@ -1590,7 +4265,7 @@
         <v>33096.57</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:2">
       <c r="A148" s="3">
         <v>40999</v>
       </c>
@@ -1598,7 +4273,7 @@
         <v>33049.71</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:2">
       <c r="A149" s="3">
         <v>41029</v>
       </c>
@@ -1606,7 +4281,7 @@
         <v>32989.129999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:2">
       <c r="A150" s="3">
         <v>41060</v>
       </c>
@@ -1614,7 +4289,7 @@
         <v>32061.089999999997</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:2">
       <c r="A151" s="3">
         <v>41090</v>
       </c>
@@ -1622,7 +4297,7 @@
         <v>32400.05</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:2">
       <c r="A152" s="3">
         <v>41121</v>
       </c>
@@ -1630,7 +4305,7 @@
         <v>32399.52</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:2">
       <c r="A153" s="3">
         <v>41152</v>
       </c>
@@ -1638,7 +4313,7 @@
         <v>32729.01</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:2">
       <c r="A154" s="3">
         <v>41182</v>
       </c>
@@ -1646,7 +4321,7 @@
         <v>32850.950000000004</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:2">
       <c r="A155" s="3">
         <v>41213</v>
       </c>
@@ -1654,7 +4329,7 @@
         <v>32874.26</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:2">
       <c r="A156" s="3">
         <v>41243</v>
       </c>
@@ -1662,7 +4337,7 @@
         <v>32976.71</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:2">
       <c r="A157" s="3">
         <v>41274</v>
       </c>
@@ -1670,7 +4345,7 @@
         <v>33115.89</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:2">
       <c r="A158" s="3">
         <v>41305</v>
       </c>
@@ -1678,7 +4353,7 @@
         <v>34100.61</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:2">
       <c r="A159" s="3">
         <v>41333</v>
       </c>
@@ -1686,7 +4361,7 @@
         <v>33954.18</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:2">
       <c r="A160" s="3">
         <v>41364</v>
       </c>
@@ -1694,7 +4369,7 @@
         <v>34426.49</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:2">
       <c r="A161" s="3">
         <v>41394</v>
       </c>
@@ -1702,7 +4377,7 @@
         <v>35344.82</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:2">
       <c r="A162" s="3">
         <v>41425</v>
       </c>
@@ -1710,7 +4385,7 @@
         <v>35148.07</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:2">
       <c r="A163" s="3">
         <v>41455</v>
       </c>
@@ -1718,7 +4393,7 @@
         <v>34966.86</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:2">
       <c r="A164" s="3">
         <v>41486</v>
       </c>
@@ -1726,7 +4401,7 @@
         <v>35478.1</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:2">
       <c r="A165" s="3">
         <v>41517</v>
       </c>
@@ -1734,7 +4409,7 @@
         <v>35530.43</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:2">
       <c r="A166" s="3">
         <v>41547</v>
       </c>
@@ -1742,7 +4417,7 @@
         <v>36626.620000000003</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:2">
       <c r="A167" s="3">
         <v>41578</v>
       </c>
@@ -1750,7 +4425,7 @@
         <v>37365.870000000003</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:2">
       <c r="A168" s="3">
         <v>41608</v>
       </c>
@@ -1758,7 +4433,7 @@
         <v>37894.509999999995</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:2">
       <c r="A169" s="3">
         <v>41639</v>
       </c>
@@ -1766,7 +4441,7 @@
         <v>38213.15</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:2">
       <c r="A170" s="3">
         <v>41670</v>
       </c>
@@ -1774,7 +4449,7 @@
         <v>38666.410000000003</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:2">
       <c r="A171" s="3">
         <v>41698</v>
       </c>
@@ -1782,7 +4457,7 @@
         <v>39137.39</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:2">
       <c r="A172" s="3">
         <v>41729</v>
       </c>
@@ -1790,7 +4465,7 @@
         <v>39480.97</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:2">
       <c r="A173" s="3">
         <v>41759</v>
       </c>
@@ -1798,7 +4473,7 @@
         <v>39787.950000000004</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:2">
       <c r="A174" s="3">
         <v>41790</v>
       </c>
@@ -1806,7 +4481,7 @@
         <v>39838.899999999994</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:2">
       <c r="A175" s="3">
         <v>41820</v>
       </c>
@@ -1814,7 +4489,7 @@
         <v>39932.130000000005</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:2">
       <c r="A176" s="3">
         <v>41851</v>
       </c>
@@ -1822,7 +4497,7 @@
         <v>39662.67</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:2">
       <c r="A177" s="3">
         <v>41882</v>
       </c>
@@ -1830,7 +4505,7 @@
         <v>39688.25</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:2">
       <c r="A178" s="3">
         <v>41912</v>
       </c>
@@ -1838,7 +4513,7 @@
         <v>38877</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:2">
       <c r="A179" s="3">
         <v>41943</v>
       </c>
@@ -1846,7 +4521,7 @@
         <v>38529.18</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:2">
       <c r="A180" s="3">
         <v>41973</v>
       </c>
@@ -1854,7 +4529,7 @@
         <v>38473.54</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:2">
       <c r="A181" s="3">
         <v>42004</v>
       </c>
@@ -1862,7 +4537,7 @@
         <v>38430.18</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:2">
       <c r="A182" s="3">
         <v>42035</v>
       </c>
@@ -1870,7 +4545,7 @@
         <v>38134.14</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:2">
       <c r="A183" s="3">
         <v>42063</v>
       </c>
@@ -1878,7 +4553,7 @@
         <v>38015.03</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:2">
       <c r="A184" s="3">
         <v>42094</v>
       </c>
@@ -1886,7 +4561,7 @@
         <v>37300.380000000005</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:2">
       <c r="A185" s="3">
         <v>42124</v>
       </c>
@@ -1894,7 +4569,7 @@
         <v>37481.42</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:2">
       <c r="A186" s="3">
         <v>42155</v>
       </c>
@@ -1902,7 +4577,7 @@
         <v>37111.43</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:2">
       <c r="A187" s="3">
         <v>42185</v>
       </c>
@@ -1910,7 +4585,7 @@
         <v>36938.379999999997</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:2">
       <c r="A188" s="3">
         <v>42216</v>
       </c>
@@ -1918,7 +4593,7 @@
         <v>36513.1</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:2">
       <c r="A189" s="3">
         <v>42247</v>
       </c>
@@ -1926,7 +4601,7 @@
         <v>35573.81</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:2">
       <c r="A190" s="3">
         <v>42277</v>
       </c>
@@ -1934,7 +4609,7 @@
         <v>35141.200000000004</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:2">
       <c r="A191" s="3">
         <v>42308</v>
       </c>
@@ -1942,7 +4617,7 @@
         <v>35255.07</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:2">
       <c r="A192" s="3">
         <v>42338</v>
       </c>
@@ -1950,7 +4625,7 @@
         <v>34382.840000000004</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:2">
       <c r="A193" s="3">
         <v>42369</v>
       </c>
@@ -1958,7 +4633,7 @@
         <v>33303.620000000003</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:2">
       <c r="A194" s="3">
         <v>42400</v>
       </c>
@@ -1966,7 +4641,7 @@
         <v>32308.929999999997</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:2">
       <c r="A195" s="3">
         <v>42429</v>
       </c>
@@ -1974,7 +4649,7 @@
         <v>32023.210000000003</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:2">
       <c r="A196" s="3">
         <v>42460</v>
       </c>
@@ -1982,7 +4657,7 @@
         <v>32125.79</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:2">
       <c r="A197" s="3">
         <v>42490</v>
       </c>
@@ -1990,7 +4665,7 @@
         <v>32196.68</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:2">
       <c r="A198" s="3">
         <v>42521</v>
       </c>
@@ -1998,7 +4673,7 @@
         <v>31917.360000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:2">
       <c r="A199" s="3">
         <v>42551</v>
       </c>
@@ -2006,7 +4681,7 @@
         <v>32051.620000000003</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:2">
       <c r="A200" s="3">
         <v>42582</v>
       </c>
@@ -2014,7 +4689,7 @@
         <v>32010.570000000003</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:2">
       <c r="A201" s="3">
         <v>42613</v>
       </c>
@@ -2022,7 +4697,7 @@
         <v>31851.670000000002</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:2">
       <c r="A202" s="3">
         <v>42643</v>
       </c>
@@ -2030,7 +4705,7 @@
         <v>31663.82</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:2">
       <c r="A203" s="3">
         <v>42674</v>
       </c>
@@ -2038,7 +4713,7 @@
         <v>31206.55</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:2">
       <c r="A204" s="3">
         <v>42704</v>
       </c>
@@ -2046,7 +4721,7 @@
         <v>30515.98</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:2">
       <c r="A205" s="3">
         <v>42735</v>
       </c>
@@ -2054,7 +4729,7 @@
         <v>30105.17</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:2">
       <c r="A206" s="3">
         <v>42766</v>
       </c>
@@ -2062,7 +4737,7 @@
         <v>29982.039999999997</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:2">
       <c r="A207" s="3">
         <v>42794</v>
       </c>
@@ -2070,7 +4745,7 @@
         <v>30051.24</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:2">
       <c r="A208" s="3">
         <v>42825</v>
       </c>
@@ -2078,7 +4753,7 @@
         <v>30090.880000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:2">
       <c r="A209" s="3">
         <v>42855</v>
       </c>
@@ -2086,7 +4761,7 @@
         <v>30295.33</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:2">
       <c r="A210" s="3">
         <v>42886</v>
       </c>
@@ -2094,7 +4769,7 @@
         <v>30535.670000000002</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:2">
       <c r="A211" s="3">
         <v>42916</v>
       </c>
@@ -2102,7 +4777,7 @@
         <v>30567.89</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:2">
       <c r="A212" s="3">
         <v>42947</v>
       </c>
@@ -2110,7 +4785,7 @@
         <v>30807.200000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:2">
       <c r="A213" s="3">
         <v>42978</v>
       </c>
@@ -2118,7 +4793,7 @@
         <v>30915.27</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:2">
       <c r="A214" s="3">
         <v>43008</v>
       </c>
@@ -2126,7 +4801,7 @@
         <v>31085.1</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:2">
       <c r="A215" s="3">
         <v>43039</v>
       </c>
@@ -2134,7 +4809,7 @@
         <v>31092.13</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:2">
       <c r="A216" s="3">
         <v>43069</v>
       </c>
@@ -2142,7 +4817,7 @@
         <v>31192.77</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:2">
       <c r="A217" s="3">
         <v>43100</v>
       </c>
@@ -2150,7 +4825,7 @@
         <v>31399.489999999998</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:2">
       <c r="A218" s="3">
         <v>43131</v>
       </c>
@@ -2158,7 +4833,7 @@
         <v>31614.57</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:2">
       <c r="A219" s="3">
         <v>43159</v>
       </c>
@@ -2166,7 +4841,7 @@
         <v>31344.820000000003</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:2">
       <c r="A220" s="3">
         <v>43190</v>
       </c>
@@ -2174,7 +4849,7 @@
         <v>31428.199999999997</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:2">
       <c r="A221" s="3">
         <v>43220</v>
       </c>
@@ -2182,7 +4857,7 @@
         <v>31248.520000000004</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:2">
       <c r="A222" s="3">
         <v>43251</v>
       </c>
@@ -2190,7 +4865,7 @@
         <v>31106.23</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:2">
       <c r="A223" s="3">
         <v>43281</v>
       </c>
@@ -2198,7 +4873,7 @@
         <v>31121.29</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:2">
       <c r="A224" s="3">
         <v>43312</v>
       </c>
@@ -2206,7 +4881,7 @@
         <v>31179.460000000003</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:2">
       <c r="A225" s="3">
         <v>43343</v>
       </c>
@@ -2214,7 +4889,7 @@
         <v>31097.16</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:2">
       <c r="A226" s="3">
         <v>43373</v>
       </c>
@@ -2222,7 +4897,7 @@
         <v>30870.25</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:2">
       <c r="A227" s="3">
         <v>43404</v>
       </c>
@@ -2230,7 +4905,7 @@
         <v>30530.979999999996</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:2">
       <c r="A228" s="3">
         <v>43434</v>
       </c>
@@ -2238,7 +4913,7 @@
         <v>30616.969999999998</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:2">
       <c r="A229" s="3">
         <v>43465</v>
       </c>
@@ -2246,7 +4921,7 @@
         <v>30727.119999999999</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:2">
       <c r="A230" s="3">
         <v>43496</v>
       </c>
@@ -2254,7 +4929,7 @@
         <v>30879.24</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:2">
       <c r="A231" s="3">
         <v>43524</v>
       </c>
@@ -2262,7 +4937,7 @@
         <v>30901.8</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:2">
       <c r="A232" s="3">
         <v>43555</v>
       </c>
@@ -2270,7 +4945,7 @@
         <v>30987.61</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:2">
       <c r="A233" s="3">
         <v>43585</v>
       </c>
@@ -2278,7 +4953,7 @@
         <v>30949.53</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:2">
       <c r="A234" s="3">
         <v>43616</v>
       </c>
@@ -2286,7 +4961,7 @@
         <v>31010.04</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:2">
       <c r="A235" s="3">
         <v>43646</v>
       </c>
@@ -2294,7 +4969,7 @@
         <v>31192.34</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:2">
       <c r="A236" s="3">
         <v>43677</v>
       </c>
@@ -2302,7 +4977,7 @@
         <v>31036.97</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:2">
       <c r="A237" s="3">
         <v>43708</v>
       </c>
@@ -2310,7 +4985,7 @@
         <v>31071.759999999998</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:2">
       <c r="A238" s="3">
         <v>43738</v>
       </c>
@@ -2318,7 +4993,7 @@
         <v>30924.31</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:2">
       <c r="A239" s="3">
         <v>43769</v>
       </c>
@@ -2326,7 +5001,7 @@
         <v>31051.61</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:2">
       <c r="A240" s="3">
         <v>43799</v>
       </c>
@@ -2334,7 +5009,7 @@
         <v>30955.910000000003</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:2">
       <c r="A241" s="3">
         <v>43830</v>
       </c>
@@ -2342,7 +5017,7 @@
         <v>31079.24</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:2">
       <c r="A242" s="3">
         <v>43861</v>
       </c>
@@ -2350,7 +5025,7 @@
         <v>31154.97</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:2">
       <c r="A243" s="3">
         <v>43890</v>
       </c>
@@ -2358,7 +5033,7 @@
         <v>31067.179999999997</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:2">
       <c r="A244" s="3">
         <v>43921</v>
       </c>
@@ -2366,7 +5041,7 @@
         <v>30606.33</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:2">
       <c r="A245" s="3">
         <v>43951</v>
       </c>
@@ -2374,7 +5049,7 @@
         <v>30914.59</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:2">
       <c r="A246" s="3">
         <v>43982</v>
       </c>
@@ -2382,7 +5057,7 @@
         <v>31016.920000000002</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:2">
       <c r="A247" s="3">
         <v>44012</v>
       </c>
@@ -2390,7 +5065,7 @@
         <v>31123.279999999999</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:2">
       <c r="A248" s="3">
         <v>44043</v>
       </c>
@@ -2398,7 +5073,7 @@
         <v>31543.91</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:2">
       <c r="A249" s="3">
         <v>44074</v>
       </c>
@@ -2406,7 +5081,7 @@
         <v>31646.09</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:2">
       <c r="A250" s="3">
         <v>44104</v>
       </c>
@@ -2414,7 +5089,7 @@
         <v>31425.620000000003</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:2">
       <c r="A251" s="3">
         <v>44135</v>
       </c>
@@ -2422,7 +5097,7 @@
         <v>31279.819999999996</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:2">
       <c r="A252" s="3">
         <v>44165</v>
       </c>
@@ -2430,7 +5105,7 @@
         <v>31784.9</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:2">
       <c r="A253" s="3">
         <v>44196</v>
       </c>
@@ -2438,7 +5113,7 @@
         <v>32165.219999999998</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:2">
       <c r="A254" s="3">
         <v>44227</v>
       </c>
@@ -2446,7 +5121,7 @@
         <v>32106.71</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:2">
       <c r="A255" s="3">
         <v>44255</v>
       </c>
@@ -2454,7 +5129,7 @@
         <v>32049.940000000002</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:2">
       <c r="A256" s="3">
         <v>44286</v>
       </c>
@@ -2462,7 +5137,7 @@
         <v>31700.289999999997</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:2">
       <c r="A257" s="3">
         <v>44316</v>
       </c>
@@ -2470,7 +5145,7 @@
         <v>31981.8</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:2">
       <c r="A258" s="3">
         <v>44347</v>
       </c>
@@ -2478,7 +5153,7 @@
         <v>32218.03</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:2">
       <c r="A259" s="3">
         <v>44377</v>
       </c>
@@ -2486,7 +5161,7 @@
         <v>32140.1</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:2">
       <c r="A260" s="3">
         <v>44408</v>
       </c>
@@ -2494,7 +5169,7 @@
         <v>32358.9</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:2">
       <c r="A261" s="3">
         <v>44439</v>
       </c>
@@ -2502,7 +5177,7 @@
         <v>32321.16</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:2">
       <c r="A262" s="3">
         <v>44469</v>
       </c>
@@ -2510,7 +5185,7 @@
         <v>32006.26</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:2">
       <c r="A263" s="3">
         <v>44500</v>
       </c>
@@ -2518,7 +5193,7 @@
         <v>32176.140000000003</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:2">
       <c r="A264" s="3">
         <v>44530</v>
       </c>
@@ -2526,7 +5201,7 @@
         <v>32223.86</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:2">
       <c r="A265" s="3">
         <v>44561</v>
       </c>
@@ -2534,7 +5209,7 @@
         <v>32501.66</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:2">
       <c r="A266" s="3">
         <v>44592</v>
       </c>
@@ -2542,7 +5217,7 @@
         <v>32216.320000000003</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:2">
       <c r="A267" s="3">
         <v>44620</v>
       </c>
@@ -2550,7 +5225,7 @@
         <v>32138.27</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:2">
       <c r="A268" s="3">
         <v>44651</v>
       </c>
@@ -2558,7 +5233,7 @@
         <v>31879.940000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:2">
       <c r="A269" s="3">
         <v>44681</v>
       </c>
@@ -2566,7 +5241,7 @@
         <v>31197.199999999997</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:2">
       <c r="A270" s="3">
         <v>44712</v>
       </c>
@@ -2574,7 +5249,7 @@
         <v>31277.800000000003</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:2">
       <c r="A271" s="3">
         <v>44742</v>
       </c>
@@ -2582,7 +5257,7 @@
         <v>30712.720000000001</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:2">
       <c r="A272" s="3">
         <v>44773</v>
       </c>
@@ -2590,7 +5265,7 @@
         <v>31040.71</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:2">
       <c r="A273" s="3">
         <v>44804</v>
       </c>
@@ -2598,7 +5273,7 @@
         <v>30548.809999999998</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:2">
       <c r="A274" s="3">
         <v>44834</v>
       </c>
@@ -2606,7 +5281,7 @@
         <v>30289.55</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:2">
       <c r="A275" s="3">
         <v>44865</v>
       </c>
@@ -2614,7 +5289,7 @@
         <v>30524.269999999997</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:2">
       <c r="A276" s="3">
         <v>44895</v>
       </c>
@@ -2622,7 +5297,7 @@
         <v>31174.880000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:2">
       <c r="A277" s="3">
         <v>44926</v>
       </c>
@@ -2630,7 +5305,7 @@
         <v>31276.91</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:2">
       <c r="A278" s="3">
         <v>44957</v>
       </c>
@@ -2638,7 +5313,7 @@
         <v>31844.62</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:2">
       <c r="A279" s="3">
         <v>44985</v>
       </c>
@@ -2646,7 +5321,7 @@
         <v>31331.530000000002</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:2">
       <c r="A280" s="3">
         <v>45016</v>
       </c>
@@ -2654,7 +5329,7 @@
         <v>31838.720000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:2">
       <c r="A281" s="3">
         <v>45046</v>
       </c>
@@ -2662,7 +5337,7 @@
         <v>32047.66</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:2">
       <c r="A282" s="3">
         <v>45077</v>
       </c>
@@ -2670,7 +5345,7 @@
         <v>31765.08</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:2">
       <c r="A283" s="3">
         <v>45107</v>
       </c>
@@ -2678,7 +5353,7 @@
         <v>31929.98</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:2">
       <c r="A284" s="3">
         <v>45138</v>
       </c>
@@ -2686,7 +5361,7 @@
         <v>32042.7</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:2">
       <c r="A285" s="3">
         <v>45169</v>
       </c>
@@ -2694,7 +5369,7 @@
         <v>31600.98</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:2">
       <c r="A286" s="3">
         <v>45199</v>
       </c>
@@ -2702,7 +5377,7 @@
         <v>31150.699999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:2">
       <c r="A287" s="3">
         <v>45230</v>
       </c>
@@ -2710,7 +5385,7 @@
         <v>31012.239999999998</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:2">
       <c r="A288" s="3">
         <v>45260</v>
       </c>
@@ -2718,7 +5393,7 @@
         <v>31718.07</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:2">
       <c r="A289" s="3">
         <v>45291</v>
       </c>
@@ -2726,7 +5401,7 @@
         <v>32379.770000000004</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:2">
       <c r="A290" s="3">
         <v>45322</v>
       </c>
@@ -2734,7 +5409,7 @@
         <v>32193.200000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:2">
       <c r="A291" s="3">
         <v>45351</v>
       </c>
@@ -2742,7 +5417,7 @@
         <v>32258.17</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:2">
       <c r="A292" s="3">
         <v>45382</v>
       </c>
@@ -2750,7 +5425,7 @@
         <v>32456.57</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:2">
       <c r="A293" s="3">
         <v>45412</v>
       </c>
@@ -2758,7 +5433,7 @@
         <v>32008.309999999998</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:2">
       <c r="A294" s="3">
         <v>45443</v>
       </c>
@@ -2766,7 +5441,7 @@
         <v>32320.39</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:2">
       <c r="A295" s="3">
         <v>45473</v>
       </c>
@@ -2774,7 +5449,7 @@
         <v>32223.579999999998</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:2">
       <c r="A296" s="3">
         <v>45504</v>
       </c>
@@ -2782,7 +5457,7 @@
         <v>32563.72</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:2">
       <c r="A297" s="3">
         <v>45535</v>
       </c>
@@ -2790,7 +5465,7 @@
         <v>32882.15</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:2">
       <c r="A298" s="3">
         <v>45565</v>
       </c>
@@ -2798,7 +5473,7 @@
         <v>33163.67</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:2">
       <c r="A299" s="3">
         <v>45596</v>
       </c>
@@ -2806,7 +5481,7 @@
         <v>32610.499999999996</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:2">
       <c r="A300" s="3">
         <v>45626</v>
       </c>
@@ -2814,13 +5489,12 @@
         <v>32658.6</v>
       </c>
     </row>
-    <row r="333" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A333" s="4" t="s">
-        <v>0</v>
-      </c>
+    <row r="333" spans="1:1">
+      <c r="A333" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>